--- a/data/trans_camb/IP16_n_R2-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP16_n_R2-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-24,11; 9,2</t>
+          <t>-23,29; 9,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-26,55; 5,53</t>
+          <t>-26,69; 6,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,19; 46,11</t>
+          <t>3,85; 47,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-30,41; 6,15</t>
+          <t>-30,17; 5,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-23,6; 17,55</t>
+          <t>-22,5; 16,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-14,99; 26,4</t>
+          <t>-13,94; 26,32</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-20,9; 2,14</t>
+          <t>-21,59; 1,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-20,37; 5,61</t>
+          <t>-19,57; 4,78</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 28,5</t>
+          <t>-0,42; 30,3</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-67,73; 50,72</t>
+          <t>-63,2; 63,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-74,53; 42,3</t>
+          <t>-78,67; 42,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,59; 260,34</t>
+          <t>9,08; 280,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-77,18; 41,62</t>
+          <t>-77,63; 34,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-63,52; 101,05</t>
+          <t>-61,35; 86,79</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-38,03; 151,98</t>
+          <t>-35,41; 141,92</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-61,85; 12,54</t>
+          <t>-62,54; 11,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-59,67; 26,66</t>
+          <t>-58,29; 24,2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 136,68</t>
+          <t>-2,7; 138,95</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-37,65; -6,92</t>
+          <t>-39,08; -9,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-39,66; -10,5</t>
+          <t>-41,45; -13,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-27,32; 4,44</t>
+          <t>-29,09; 1,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-40,18; -15,47</t>
+          <t>-41,21; -16,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-44,45; -19,01</t>
+          <t>-46,25; -18,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-15,43; 17,15</t>
+          <t>-15,72; 17,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-35,63; -16,84</t>
+          <t>-36,7; -17,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-38,98; -19,74</t>
+          <t>-39,36; -19,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-16,27; 5,5</t>
+          <t>-17,15; 5,71</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-76,56; -20,31</t>
+          <t>-79,5; -26,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-83,06; -32,19</t>
+          <t>-82,78; -35,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-57,1; 14,3</t>
+          <t>-61,38; 4,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-83,57; -44,19</t>
+          <t>-83,31; -47,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-91,27; -50,81</t>
+          <t>-91,78; -51,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-32,88; 52,5</t>
+          <t>-32,07; 52,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-77,32; -46,84</t>
+          <t>-77,76; -46,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-83,09; -52,94</t>
+          <t>-83,05; -52,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-35,86; 15,5</t>
+          <t>-36,86; 17,25</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-48,04; -10,77</t>
+          <t>-47,05; -9,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-44,12; -8,07</t>
+          <t>-46,78; -10,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,51; 33,07</t>
+          <t>-11,7; 29,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-52,94; -15,76</t>
+          <t>-51,32; -14,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-49,19; -11,69</t>
+          <t>-48,82; -12,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-34,74; 3,89</t>
+          <t>-35,9; 4,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-43,7; -18,77</t>
+          <t>-43,98; -16,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-42,47; -16,12</t>
+          <t>-42,1; -15,76</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-18,95; 9,42</t>
+          <t>-19,06; 10,33</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-90,6; -32,76</t>
+          <t>-91,47; -32,08</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-88,97; -24,09</t>
+          <t>-90,39; -30,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-19,59; 151,68</t>
+          <t>-22,5; 110,71</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-95,18; -39,61</t>
+          <t>-100,0; -40,87</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-90,81; -29,35</t>
+          <t>-91,86; -39,68</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-65,31; 16,8</t>
+          <t>-68,83; 16,18</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-89,72; -53,79</t>
+          <t>-89,33; -46,92</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-86,59; -48,73</t>
+          <t>-85,42; -48,43</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-39,45; 32,21</t>
+          <t>-39,24; 30,12</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-40,24; -0,23</t>
+          <t>-39,22; 1,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-55,9; -23,2</t>
+          <t>-55,57; -21,73</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-50,17; -12,24</t>
+          <t>-50,26; -13,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-43,75; -9,95</t>
+          <t>-42,03; -9,29</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-46,13; -9,48</t>
+          <t>-45,43; -10,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-29,48; 4,98</t>
+          <t>-29,17; 4,58</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-35,8; -9,98</t>
+          <t>-36,35; -9,51</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-46,53; -21,79</t>
+          <t>-47,45; -22,23</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-37,29; -9,81</t>
+          <t>-36,87; -9,12</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-74,11; 3,54</t>
+          <t>-73,37; 5,14</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -54,6</t>
+          <t>-100,0; -56,62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-88,75; -35,46</t>
+          <t>-90,87; -38,36</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-83,51; -25,52</t>
+          <t>-82,67; -24,84</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-88,51; -24,42</t>
+          <t>-87,74; -19,16</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-55,69; 14,26</t>
+          <t>-55,51; 12,45</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-72,58; -26,13</t>
+          <t>-73,06; -25,07</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-90,75; -53,79</t>
+          <t>-90,49; -53,55</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-74,87; -26,85</t>
+          <t>-71,81; -24,09</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-28,63; -10,7</t>
+          <t>-29,14; -12,02</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-34,38; -17,62</t>
+          <t>-33,92; -17,92</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-24,25; 0,87</t>
+          <t>-22,94; 0,87</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-34,67; -18,4</t>
+          <t>-34,22; -18,22</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-34,3; -17,67</t>
+          <t>-33,04; -17,31</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-15,41; 3,21</t>
+          <t>-14,84; 3,11</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-29,05; -17,3</t>
+          <t>-29,36; -16,78</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-31,7; -20,09</t>
+          <t>-31,74; -20,17</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-16,51; -1,25</t>
+          <t>-18,09; -1,19</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-66,58; -32,2</t>
+          <t>-67,33; -34,64</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-78,25; -50,6</t>
+          <t>-79,05; -52,49</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-57,26; 2,23</t>
+          <t>-55,0; 2,17</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-77,79; -51,18</t>
+          <t>-76,48; -50,67</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-76,94; -47,28</t>
+          <t>-76,58; -48,5</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-34,54; 8,91</t>
+          <t>-33,44; 9,03</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-69,38; -47,67</t>
+          <t>-69,16; -48,71</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-75,28; -55,25</t>
+          <t>-75,02; -56,05</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-39,98; -4,15</t>
+          <t>-41,98; -3,37</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16_n_R2-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP16_n_R2-Edad-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumen más de dos medicamentos</t>
+          <t>Menores que consumieron más de dos medicamentos en las últimas 2 semanas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-12,13</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-4,0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6,62</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-6,85</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-10,3</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>25,42</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-12,13</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-4,0</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,12</t>
+          <t>26,59</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>14,35</t>
+          <t>15,68</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-23,29; 9,82</t>
+          <t>-28,87; 4,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-26,69; 6,95</t>
+          <t>-23,31; 14,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,85; 47,43</t>
+          <t>-14,07; 26,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-30,17; 5,06</t>
+          <t>-23,42; 9,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-22,5; 16,22</t>
+          <t>-27,22; 6,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,94; 26,32</t>
+          <t>2,88; 47,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-21,59; 1,97</t>
+          <t>-21,71; 2,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-19,57; 4,78</t>
+          <t>-20,15; 6,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 30,3</t>
+          <t>-0,16; 29,97</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-42,15%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-13,89%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>23,01%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-25,88%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-38,88%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>96,02%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-42,15%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-13,89%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>100,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>56,73%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-63,2; 63,97</t>
+          <t>-75,92; 34,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-78,67; 42,8</t>
+          <t>-64,04; 70,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,08; 280,95</t>
+          <t>-38,01; 140,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-77,63; 34,26</t>
+          <t>-64,62; 58,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-61,35; 86,79</t>
+          <t>-76,8; 45,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-35,41; 141,92</t>
+          <t>5,58; 255,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-62,54; 11,13</t>
+          <t>-61,79; 12,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-58,29; 24,2</t>
+          <t>-60,6; 33,08</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 138,95</t>
+          <t>-0,88; 146,91</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-28,39</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-31,94</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2,8</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-23,87</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-26,46</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-13,09</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-28,39</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-31,94</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,94</t>
+          <t>-11,46</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-5,91</t>
+          <t>-4,31</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-39,08; -9,46</t>
+          <t>-40,78; -15,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-41,45; -13,26</t>
+          <t>-44,17; -18,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-29,09; 1,53</t>
+          <t>-13,36; 18,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-41,21; -16,85</t>
+          <t>-37,21; -8,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-46,25; -18,83</t>
+          <t>-40,3; -11,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-15,72; 17,29</t>
+          <t>-26,52; 4,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-36,7; -17,08</t>
+          <t>-36,38; -16,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-39,36; -19,32</t>
+          <t>-39,0; -19,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-17,15; 5,71</t>
+          <t>-16,24; 7,49</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-68,98%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-77,62%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6,81%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-58,18%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-64,49%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-31,92%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-68,98%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-77,62%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>-27,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-14,37%</t>
+          <t>-10,48%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-79,5; -26,98</t>
+          <t>-84,09; -43,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-82,78; -35,91</t>
+          <t>-91,59; -53,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-61,38; 4,56</t>
+          <t>-28,5; 56,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-83,31; -47,09</t>
+          <t>-78,05; -25,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-91,78; -51,04</t>
+          <t>-84,07; -34,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-32,07; 52,93</t>
+          <t>-56,81; 14,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-77,76; -46,6</t>
+          <t>-76,51; -46,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-83,05; -52,41</t>
+          <t>-84,47; -54,09</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-36,86; 17,25</t>
+          <t>-35,46; 22,15</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-33,22</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-30,78</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-15,63</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-27,94</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-27,33</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>10,11</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-33,22</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-30,78</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-16,3</t>
+          <t>9,73</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-4,4</t>
+          <t>-3,81</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-47,05; -9,74</t>
+          <t>-51,56; -14,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-46,78; -10,12</t>
+          <t>-48,23; -13,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,7; 29,49</t>
+          <t>-37,9; 3,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-51,32; -14,14</t>
+          <t>-48,81; -9,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-48,82; -12,02</t>
+          <t>-45,82; -9,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-35,9; 4,61</t>
+          <t>-12,22; 30,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-43,98; -16,1</t>
+          <t>-44,73; -17,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-42,1; -15,76</t>
+          <t>-42,34; -14,67</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-19,06; 10,33</t>
+          <t>-18,84; 11,33</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-79,19%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-73,37%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-37,26%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-71,89%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-70,33%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>26,0%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-79,19%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-73,37%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-38,84%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-10,88%</t>
+          <t>-9,43%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-91,47; -32,08</t>
+          <t>-95,52; -38,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-90,39; -30,56</t>
+          <t>-91,42; -34,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-22,5; 110,71</t>
+          <t>-69,95; 10,7</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -40,87</t>
+          <t>-91,01; -22,14</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-91,86; -39,68</t>
+          <t>-89,73; -25,39</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-68,83; 16,18</t>
+          <t>-25,11; 116,43</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-89,33; -46,92</t>
+          <t>-88,99; -51,87</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-85,42; -48,43</t>
+          <t>-85,59; -45,01</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-39,24; 30,12</t>
+          <t>-38,65; 37,21</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-27,26</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-30,27</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-12,77</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-20,24</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-39,22</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-30,78</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-27,26</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-30,27</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-12,63</t>
+          <t>-21,92</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-22,54</t>
+          <t>-16,84</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-39,22; 1,03</t>
+          <t>-43,06; -9,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-55,57; -21,73</t>
+          <t>-47,96; -12,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-50,26; -13,29</t>
+          <t>-28,8; 4,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-42,03; -9,29</t>
+          <t>-39,16; -1,18</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-45,43; -10,62</t>
+          <t>-55,89; -23,47</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-29,17; 4,58</t>
+          <t>-39,09; -2,85</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-36,35; -9,51</t>
+          <t>-37,82; -9,99</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-47,45; -22,23</t>
+          <t>-45,61; -21,39</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-36,87; -9,12</t>
+          <t>-28,54; -4,03</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-60,57%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-67,27%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-28,37%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-44,89%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-86,98%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-68,27%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-60,57%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-67,27%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-28,07%</t>
+          <t>-48,61%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-50,05%</t>
+          <t>-37,39%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-73,37; 5,14</t>
+          <t>-84,26; -20,31</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -56,62</t>
+          <t>-88,34; -19,14</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-90,87; -38,36</t>
+          <t>-55,14; 11,11</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-82,67; -24,84</t>
+          <t>-74,78; -0,2</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-87,74; -19,16</t>
+          <t>-100,0; -52,24</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-55,51; 12,45</t>
+          <t>-71,34; -5,39</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-73,06; -25,07</t>
+          <t>-72,63; -24,56</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-90,49; -53,55</t>
+          <t>-90,1; -51,75</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-71,81; -24,09</t>
+          <t>-56,0; -10,54</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-26,01</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-26,0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-5,87</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-20,33</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-25,71</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-9,75</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-26,01</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-26,0</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-6,2</t>
+          <t>-3,55</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-7,99</t>
+          <t>-4,79</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-29,14; -12,02</t>
+          <t>-33,59; -17,53</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-33,92; -17,92</t>
+          <t>-33,68; -16,99</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-22,94; 0,87</t>
+          <t>-14,16; 4,27</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-34,22; -18,22</t>
+          <t>-28,62; -11,14</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-33,04; -17,31</t>
+          <t>-34,7; -18,28</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-14,84; 3,11</t>
+          <t>-12,46; 5,4</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-29,36; -16,78</t>
+          <t>-29,1; -17,2</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-31,74; -20,17</t>
+          <t>-31,9; -19,75</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-18,09; -1,19</t>
+          <t>-11,18; 2,52</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-65,38%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-65,35%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-14,74%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-53,15%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-67,21%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-25,48%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-65,38%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-65,35%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-15,57%</t>
+          <t>-9,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-20,46%</t>
+          <t>-12,26%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-67,33; -34,64</t>
+          <t>-76,87; -49,48</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-79,05; -52,49</t>
+          <t>-76,87; -47,96</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-55,0; 2,17</t>
+          <t>-31,86; 12,88</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-76,48; -50,67</t>
+          <t>-66,91; -33,23</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-76,58; -48,5</t>
+          <t>-80,14; -51,99</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-33,44; 9,03</t>
+          <t>-28,72; 16,59</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-69,16; -48,71</t>
+          <t>-69,57; -48,11</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-75,02; -56,05</t>
+          <t>-75,38; -54,76</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-41,98; -3,37</t>
+          <t>-26,59; 7,69</t>
         </is>
       </c>
     </row>
